--- a/backend/all_invoices.xlsx
+++ b/backend/all_invoices.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="100">
   <si>
     <t>transactionStatus</t>
   </si>
@@ -124,6 +124,9 @@
     <t>FRIGOBLOCK GmbH</t>
   </si>
   <si>
+    <t>Kelsifahr, Inc.</t>
+  </si>
+  <si>
     <t>Tychy</t>
   </si>
   <si>
@@ -133,6 +136,9 @@
     <t>Postf./P.O.Box 11 02 39, D-45332 Essen, Weidkamp 274, D-45356 Essen</t>
   </si>
   <si>
+    <t>739 Kasota Ave SE, Minneapolis, MN 55414</t>
+  </si>
+  <si>
     <t>Tychy Murarska 17a</t>
   </si>
   <si>
@@ -142,7 +148,7 @@
     <t>823014</t>
   </si>
   <si>
-    <t>DUNS: 427364709</t>
+    <t>DUNS: 427364709 NR REJ. BDO: 000021454</t>
   </si>
   <si>
     <t>NET 90</t>
@@ -151,6 +157,9 @@
     <t>45 Tage netto</t>
   </si>
   <si>
+    <t>Net 30</t>
+  </si>
+  <si>
     <t>Transfer (30 days)</t>
   </si>
   <si>
@@ -166,6 +175,9 @@
     <t>EB-0062849</t>
   </si>
   <si>
+    <t>315648-0</t>
+  </si>
+  <si>
     <t>ZS/1948/2024</t>
   </si>
   <si>
@@ -175,12 +187,18 @@
     <t>2025-08-11</t>
   </si>
   <si>
+    <t>2024-09-10</t>
+  </si>
+  <si>
     <t>2024-12-17</t>
   </si>
   <si>
     <t>401105</t>
   </si>
   <si>
+    <t>55414</t>
+  </si>
+  <si>
     <t>43-100</t>
   </si>
   <si>
@@ -218,6 +236,15 @@
   </si>
   <si>
     <t>4E27317H01</t>
+  </si>
+  <si>
+    <t>A0001487540 Rev C</t>
+  </si>
+  <si>
+    <t>A0001501260 Rev C</t>
+  </si>
+  <si>
+    <t>A0001839296 Rev A</t>
   </si>
   <si>
     <t>SA3284487_P1</t>
@@ -281,9 +308,6 @@
   </si>
   <si>
     <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>2025-07-04</t>
   </si>
   <si>
     <t>2025-05-12</t>
@@ -650,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE23"/>
+  <dimension ref="A1:AE26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31">
@@ -756,46 +780,46 @@
         <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Q2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="R2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="T2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="U2">
         <v>16000</v>
       </c>
       <c r="V2" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="W2">
         <v>1.24</v>
       </c>
       <c r="AA2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AD2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -806,46 +830,46 @@
         <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Q3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="R3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="T3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="U3">
         <v>3600</v>
       </c>
       <c r="V3" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="W3">
         <v>0.76</v>
       </c>
       <c r="AA3" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="AD3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:31">
@@ -856,46 +880,46 @@
         <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Q4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="R4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="T4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="U4">
         <v>2400</v>
       </c>
       <c r="V4" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="W4">
         <v>0.76</v>
       </c>
       <c r="AA4" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="AD4" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE4" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -906,46 +930,46 @@
         <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Q5" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="R5" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="T5" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="U5">
         <v>2800</v>
       </c>
       <c r="V5" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="W5">
         <v>0.76</v>
       </c>
       <c r="AA5" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="AD5" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE5" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -956,46 +980,46 @@
         <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Q6" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="R6" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="T6" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="U6">
         <v>5600</v>
       </c>
       <c r="V6" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="W6">
         <v>0.76</v>
       </c>
       <c r="AA6" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="AD6" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE6" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -1006,46 +1030,46 @@
         <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Q7" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="R7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="T7" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="U7">
         <v>2000</v>
       </c>
       <c r="V7" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="W7">
         <v>0.76</v>
       </c>
       <c r="AA7" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="AD7" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE7" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:31">
@@ -1056,46 +1080,46 @@
         <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O8" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Q8" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="R8" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="T8" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="U8">
         <v>1200</v>
       </c>
       <c r="V8" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="W8">
         <v>0.76</v>
       </c>
       <c r="AA8" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="AD8" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE8" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -1106,46 +1130,46 @@
         <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O9" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Q9" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="R9" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="T9" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="U9">
         <v>2200</v>
       </c>
       <c r="V9" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="W9">
         <v>0.76</v>
       </c>
       <c r="AA9" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="AD9" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE9" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -1156,46 +1180,46 @@
         <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O10" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Q10" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="R10" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="T10" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="U10">
         <v>3000</v>
       </c>
       <c r="V10" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="W10">
         <v>0.88</v>
       </c>
       <c r="AA10" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="AD10" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE10" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -1206,46 +1230,46 @@
         <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O11" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Q11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="R11" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="T11" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="U11">
         <v>2000</v>
       </c>
       <c r="V11" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="W11">
         <v>0.88</v>
       </c>
       <c r="AA11" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="AD11" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE11" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -1256,46 +1280,46 @@
         <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N12" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Q12" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="R12" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="T12" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="U12">
         <v>3000</v>
       </c>
       <c r="V12" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="W12">
         <v>0.88</v>
       </c>
       <c r="AA12" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="AD12" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE12" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -1306,52 +1330,52 @@
         <v>35</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O13" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Q13" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="R13" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="T13" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="U13">
         <v>100</v>
       </c>
       <c r="V13" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="W13">
         <v>4.31</v>
       </c>
       <c r="Z13" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AA13" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AD13" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE13" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:31">
@@ -1362,52 +1386,52 @@
         <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O14" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Q14" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="R14" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="T14" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="U14">
         <v>100</v>
       </c>
       <c r="V14" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="W14">
         <v>14.79</v>
       </c>
       <c r="Z14" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AA14" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AD14" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE14" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:31">
@@ -1418,52 +1442,52 @@
         <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N15" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Q15" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="R15" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="T15" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="U15">
         <v>100</v>
       </c>
       <c r="V15" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="W15">
         <v>2.76</v>
       </c>
       <c r="Z15" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AA15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AD15" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE15" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:31">
@@ -1474,52 +1498,52 @@
         <v>35</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H16" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O16" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Q16" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="R16" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="T16" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="U16">
         <v>100</v>
       </c>
       <c r="V16" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="W16">
         <v>11.76</v>
       </c>
       <c r="Z16" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AA16" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AD16" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE16" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="3:31">
@@ -1530,220 +1554,184 @@
         <v>35</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H17" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N17" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Q17" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="R17" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="T17" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="U17">
         <v>150</v>
       </c>
       <c r="V17" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="W17">
         <v>1.06</v>
       </c>
       <c r="Z17" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AA17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AD17" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE17" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="3:31">
       <c r="C18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
         <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H18" t="s">
         <v>47</v>
       </c>
       <c r="N18" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O18" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q18" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="R18" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="T18" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="U18">
-        <v>7000</v>
-      </c>
-      <c r="V18" t="s">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="W18">
-        <v>39</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>79</v>
+        <v>5.74</v>
       </c>
       <c r="AA18" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="AD18" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE18" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="3:31">
       <c r="C19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
         <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
-      </c>
-      <c r="F19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G19" t="s">
-        <v>45</v>
-      </c>
-      <c r="H19" t="s">
         <v>47</v>
       </c>
       <c r="N19" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O19" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q19" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="R19" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="T19" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="U19">
-        <v>15000</v>
-      </c>
-      <c r="V19" t="s">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="W19">
-        <v>22</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>79</v>
+        <v>5.36</v>
       </c>
       <c r="AA19" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="AD19" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE19" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="3:31">
       <c r="C20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
         <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G20" t="s">
-        <v>45</v>
-      </c>
-      <c r="H20" t="s">
         <v>47</v>
       </c>
       <c r="N20" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O20" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q20" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="R20" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="T20" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="U20">
-        <v>15000</v>
-      </c>
-      <c r="V20" t="s">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="W20">
-        <v>23</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>79</v>
+        <v>3.5</v>
       </c>
       <c r="AA20" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="AD20" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE20" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="3:31">
@@ -1751,52 +1739,55 @@
         <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" t="s">
+        <v>48</v>
+      </c>
+      <c r="H21" t="s">
+        <v>50</v>
+      </c>
+      <c r="N21" t="s">
+        <v>54</v>
+      </c>
+      <c r="O21" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>61</v>
+      </c>
+      <c r="R21" t="s">
+        <v>62</v>
+      </c>
+      <c r="T21" t="s">
+        <v>77</v>
+      </c>
+      <c r="U21">
+        <v>7000</v>
+      </c>
+      <c r="V21" t="s">
+        <v>82</v>
+      </c>
+      <c r="W21">
         <v>39</v>
       </c>
-      <c r="F21" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" t="s">
-        <v>45</v>
-      </c>
-      <c r="H21" t="s">
-        <v>47</v>
-      </c>
-      <c r="N21" t="s">
-        <v>50</v>
-      </c>
-      <c r="O21" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>55</v>
-      </c>
-      <c r="R21" t="s">
-        <v>56</v>
-      </c>
-      <c r="T21" t="s">
-        <v>71</v>
-      </c>
-      <c r="U21">
-        <v>1000</v>
-      </c>
-      <c r="V21" t="s">
-        <v>73</v>
-      </c>
-      <c r="W21">
-        <v>680</v>
-      </c>
       <c r="Z21" t="s">
-        <v>80</v>
+        <v>88</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>97</v>
       </c>
       <c r="AD21" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE21" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="3:31">
@@ -1804,52 +1795,55 @@
         <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E22" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G22" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H22" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N22" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="O22" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="Q22" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="R22" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="T22" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="U22">
-        <v>1000</v>
+        <v>15000</v>
       </c>
       <c r="V22" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="W22">
-        <v>600</v>
+        <v>22</v>
       </c>
       <c r="Z22" t="s">
-        <v>81</v>
+        <v>88</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>97</v>
       </c>
       <c r="AD22" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AE22" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="3:31">
@@ -1857,52 +1851,214 @@
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G23" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H23" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N23" t="s">
+        <v>54</v>
+      </c>
+      <c r="O23" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>61</v>
+      </c>
+      <c r="R23" t="s">
+        <v>62</v>
+      </c>
+      <c r="T23" t="s">
+        <v>79</v>
+      </c>
+      <c r="U23">
+        <v>15000</v>
+      </c>
+      <c r="V23" t="s">
+        <v>82</v>
+      </c>
+      <c r="W23">
+        <v>23</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31">
+      <c r="C24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H24" t="s">
         <v>50</v>
       </c>
-      <c r="O23" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>55</v>
-      </c>
-      <c r="R23" t="s">
-        <v>56</v>
-      </c>
-      <c r="T23" t="s">
-        <v>71</v>
-      </c>
-      <c r="U23">
+      <c r="N24" t="s">
+        <v>54</v>
+      </c>
+      <c r="O24" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>61</v>
+      </c>
+      <c r="R24" t="s">
+        <v>62</v>
+      </c>
+      <c r="T24" t="s">
+        <v>80</v>
+      </c>
+      <c r="U24">
         <v>1000</v>
       </c>
-      <c r="V23" t="s">
-        <v>73</v>
-      </c>
-      <c r="W23">
+      <c r="V24" t="s">
+        <v>82</v>
+      </c>
+      <c r="W24">
+        <v>680</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31">
+      <c r="C25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" t="s">
+        <v>50</v>
+      </c>
+      <c r="N25" t="s">
+        <v>54</v>
+      </c>
+      <c r="O25" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>61</v>
+      </c>
+      <c r="R25" t="s">
+        <v>62</v>
+      </c>
+      <c r="T25" t="s">
+        <v>80</v>
+      </c>
+      <c r="U25">
+        <v>1000</v>
+      </c>
+      <c r="V25" t="s">
+        <v>82</v>
+      </c>
+      <c r="W25">
+        <v>600</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31">
+      <c r="C26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" t="s">
+        <v>41</v>
+      </c>
+      <c r="F26" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" t="s">
+        <v>48</v>
+      </c>
+      <c r="H26" t="s">
+        <v>50</v>
+      </c>
+      <c r="N26" t="s">
+        <v>54</v>
+      </c>
+      <c r="O26" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>61</v>
+      </c>
+      <c r="R26" t="s">
+        <v>62</v>
+      </c>
+      <c r="T26" t="s">
+        <v>80</v>
+      </c>
+      <c r="U26">
+        <v>1000</v>
+      </c>
+      <c r="V26" t="s">
+        <v>82</v>
+      </c>
+      <c r="W26">
         <v>560</v>
       </c>
-      <c r="Z23" t="s">
-        <v>82</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>90</v>
-      </c>
-      <c r="AE23" t="s">
+      <c r="Z26" t="s">
         <v>91</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/backend/all_invoices.xlsx
+++ b/backend/all_invoices.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
   <si>
     <t>transactionStatus</t>
   </si>
@@ -124,9 +124,6 @@
     <t>FRIGOBLOCK GmbH</t>
   </si>
   <si>
-    <t>Kelsifahr, Inc.</t>
-  </si>
-  <si>
     <t>Tychy</t>
   </si>
   <si>
@@ -136,9 +133,6 @@
     <t>Postf./P.O.Box 11 02 39, D-45332 Essen, Weidkamp 274, D-45356 Essen</t>
   </si>
   <si>
-    <t>739 Kasota Ave SE, Minneapolis, MN 55414</t>
-  </si>
-  <si>
     <t>Tychy Murarska 17a</t>
   </si>
   <si>
@@ -157,9 +151,6 @@
     <t>45 Tage netto</t>
   </si>
   <si>
-    <t>Net 30</t>
-  </si>
-  <si>
     <t>Transfer (30 days)</t>
   </si>
   <si>
@@ -175,9 +166,6 @@
     <t>EB-0062849</t>
   </si>
   <si>
-    <t>315648-0</t>
-  </si>
-  <si>
     <t>ZS/1948/2024</t>
   </si>
   <si>
@@ -187,18 +175,12 @@
     <t>2025-08-11</t>
   </si>
   <si>
-    <t>2024-09-10</t>
-  </si>
-  <si>
     <t>2024-12-17</t>
   </si>
   <si>
     <t>401105</t>
   </si>
   <si>
-    <t>55414</t>
-  </si>
-  <si>
     <t>43-100</t>
   </si>
   <si>
@@ -236,15 +218,6 @@
   </si>
   <si>
     <t>4E27317H01</t>
-  </si>
-  <si>
-    <t>A0001487540 Rev C</t>
-  </si>
-  <si>
-    <t>A0001501260 Rev C</t>
-  </si>
-  <si>
-    <t>A0001839296 Rev A</t>
   </si>
   <si>
     <t>SA3284487_P1</t>
@@ -308,6 +281,9 @@
   </si>
   <si>
     <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>2025-05-12</t>
@@ -674,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE26"/>
+  <dimension ref="A1:AE23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31">
@@ -780,46 +756,46 @@
         <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" t="s">
         <v>51</v>
       </c>
-      <c r="O2" t="s">
-        <v>55</v>
-      </c>
       <c r="Q2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="T2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="U2">
         <v>16000</v>
       </c>
       <c r="V2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="W2">
         <v>1.24</v>
       </c>
       <c r="AA2" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AD2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -830,46 +806,46 @@
         <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O3" t="s">
         <v>51</v>
       </c>
-      <c r="O3" t="s">
-        <v>55</v>
-      </c>
       <c r="Q3" t="s">
+        <v>54</v>
+      </c>
+      <c r="R3" t="s">
+        <v>56</v>
+      </c>
+      <c r="T3" t="s">
         <v>59</v>
-      </c>
-      <c r="R3" t="s">
-        <v>62</v>
-      </c>
-      <c r="T3" t="s">
-        <v>65</v>
       </c>
       <c r="U3">
         <v>3600</v>
       </c>
       <c r="V3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="W3">
         <v>0.76</v>
       </c>
       <c r="AA3" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="AD3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:31">
@@ -880,46 +856,46 @@
         <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
+        <v>48</v>
+      </c>
+      <c r="O4" t="s">
         <v>51</v>
       </c>
-      <c r="O4" t="s">
-        <v>55</v>
-      </c>
       <c r="Q4" t="s">
+        <v>54</v>
+      </c>
+      <c r="R4" t="s">
+        <v>56</v>
+      </c>
+      <c r="T4" t="s">
         <v>59</v>
-      </c>
-      <c r="R4" t="s">
-        <v>62</v>
-      </c>
-      <c r="T4" t="s">
-        <v>65</v>
       </c>
       <c r="U4">
         <v>2400</v>
       </c>
       <c r="V4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="W4">
         <v>0.76</v>
       </c>
       <c r="AA4" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="AD4" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -930,46 +906,46 @@
         <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
+        <v>48</v>
+      </c>
+      <c r="O5" t="s">
         <v>51</v>
       </c>
-      <c r="O5" t="s">
-        <v>55</v>
-      </c>
       <c r="Q5" t="s">
+        <v>54</v>
+      </c>
+      <c r="R5" t="s">
+        <v>56</v>
+      </c>
+      <c r="T5" t="s">
         <v>59</v>
-      </c>
-      <c r="R5" t="s">
-        <v>62</v>
-      </c>
-      <c r="T5" t="s">
-        <v>65</v>
       </c>
       <c r="U5">
         <v>2800</v>
       </c>
       <c r="V5" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="W5">
         <v>0.76</v>
       </c>
       <c r="AA5" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AD5" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE5" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -980,46 +956,46 @@
         <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
+        <v>48</v>
+      </c>
+      <c r="O6" t="s">
         <v>51</v>
       </c>
-      <c r="O6" t="s">
-        <v>55</v>
-      </c>
       <c r="Q6" t="s">
+        <v>54</v>
+      </c>
+      <c r="R6" t="s">
+        <v>56</v>
+      </c>
+      <c r="T6" t="s">
         <v>59</v>
-      </c>
-      <c r="R6" t="s">
-        <v>62</v>
-      </c>
-      <c r="T6" t="s">
-        <v>65</v>
       </c>
       <c r="U6">
         <v>5600</v>
       </c>
       <c r="V6" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="W6">
         <v>0.76</v>
       </c>
       <c r="AA6" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="AD6" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE6" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -1030,46 +1006,46 @@
         <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
+        <v>48</v>
+      </c>
+      <c r="O7" t="s">
         <v>51</v>
       </c>
-      <c r="O7" t="s">
-        <v>55</v>
-      </c>
       <c r="Q7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R7" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="T7" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="U7">
         <v>2000</v>
       </c>
       <c r="V7" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="W7">
         <v>0.76</v>
       </c>
       <c r="AA7" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="AD7" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE7" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:31">
@@ -1080,46 +1056,46 @@
         <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N8" t="s">
+        <v>48</v>
+      </c>
+      <c r="O8" t="s">
         <v>51</v>
       </c>
-      <c r="O8" t="s">
-        <v>55</v>
-      </c>
       <c r="Q8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R8" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="T8" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="U8">
         <v>1200</v>
       </c>
       <c r="V8" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="W8">
         <v>0.76</v>
       </c>
       <c r="AA8" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AD8" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE8" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -1130,46 +1106,46 @@
         <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N9" t="s">
+        <v>48</v>
+      </c>
+      <c r="O9" t="s">
         <v>51</v>
       </c>
-      <c r="O9" t="s">
-        <v>55</v>
-      </c>
       <c r="Q9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R9" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="T9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="U9">
         <v>2200</v>
       </c>
       <c r="V9" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="W9">
         <v>0.76</v>
       </c>
       <c r="AA9" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="AD9" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE9" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -1180,46 +1156,46 @@
         <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N10" t="s">
+        <v>48</v>
+      </c>
+      <c r="O10" t="s">
         <v>51</v>
       </c>
-      <c r="O10" t="s">
-        <v>55</v>
-      </c>
       <c r="Q10" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R10" t="s">
+        <v>56</v>
+      </c>
+      <c r="T10" t="s">
         <v>62</v>
-      </c>
-      <c r="T10" t="s">
-        <v>68</v>
       </c>
       <c r="U10">
         <v>3000</v>
       </c>
       <c r="V10" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="W10">
         <v>0.88</v>
       </c>
       <c r="AA10" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="AD10" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE10" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -1230,46 +1206,46 @@
         <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N11" t="s">
+        <v>48</v>
+      </c>
+      <c r="O11" t="s">
         <v>51</v>
       </c>
-      <c r="O11" t="s">
-        <v>55</v>
-      </c>
       <c r="Q11" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R11" t="s">
+        <v>56</v>
+      </c>
+      <c r="T11" t="s">
         <v>62</v>
-      </c>
-      <c r="T11" t="s">
-        <v>68</v>
       </c>
       <c r="U11">
         <v>2000</v>
       </c>
       <c r="V11" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="W11">
         <v>0.88</v>
       </c>
       <c r="AA11" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AD11" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE11" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -1280,46 +1256,46 @@
         <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N12" t="s">
+        <v>48</v>
+      </c>
+      <c r="O12" t="s">
         <v>51</v>
       </c>
-      <c r="O12" t="s">
-        <v>55</v>
-      </c>
       <c r="Q12" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R12" t="s">
+        <v>56</v>
+      </c>
+      <c r="T12" t="s">
         <v>62</v>
-      </c>
-      <c r="T12" t="s">
-        <v>68</v>
       </c>
       <c r="U12">
         <v>3000</v>
       </c>
       <c r="V12" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="W12">
         <v>0.88</v>
       </c>
       <c r="AA12" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="AD12" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE12" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -1330,52 +1306,52 @@
         <v>35</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" t="s">
         <v>46</v>
       </c>
-      <c r="H13" t="s">
+      <c r="N13" t="s">
         <v>49</v>
       </c>
-      <c r="N13" t="s">
+      <c r="O13" t="s">
         <v>52</v>
       </c>
-      <c r="O13" t="s">
-        <v>56</v>
-      </c>
       <c r="Q13" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R13" t="s">
+        <v>57</v>
+      </c>
+      <c r="T13" t="s">
         <v>63</v>
-      </c>
-      <c r="T13" t="s">
-        <v>69</v>
       </c>
       <c r="U13">
         <v>100</v>
       </c>
       <c r="V13" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="W13">
         <v>4.31</v>
       </c>
       <c r="Z13" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AA13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="AD13" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE13" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:31">
@@ -1386,52 +1362,52 @@
         <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" t="s">
         <v>46</v>
       </c>
-      <c r="H14" t="s">
+      <c r="N14" t="s">
         <v>49</v>
       </c>
-      <c r="N14" t="s">
+      <c r="O14" t="s">
         <v>52</v>
       </c>
-      <c r="O14" t="s">
-        <v>56</v>
-      </c>
       <c r="Q14" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R14" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="T14" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="U14">
         <v>100</v>
       </c>
       <c r="V14" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="W14">
         <v>14.79</v>
       </c>
       <c r="Z14" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AA14" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="AD14" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE14" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:31">
@@ -1442,52 +1418,52 @@
         <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" t="s">
         <v>46</v>
       </c>
-      <c r="H15" t="s">
+      <c r="N15" t="s">
         <v>49</v>
       </c>
-      <c r="N15" t="s">
+      <c r="O15" t="s">
         <v>52</v>
       </c>
-      <c r="O15" t="s">
-        <v>56</v>
-      </c>
       <c r="Q15" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R15" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="T15" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="U15">
         <v>100</v>
       </c>
       <c r="V15" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="W15">
         <v>2.76</v>
       </c>
       <c r="Z15" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AA15" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="AD15" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE15" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:31">
@@ -1498,52 +1474,52 @@
         <v>35</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G16" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" t="s">
         <v>46</v>
       </c>
-      <c r="H16" t="s">
+      <c r="N16" t="s">
         <v>49</v>
       </c>
-      <c r="N16" t="s">
+      <c r="O16" t="s">
         <v>52</v>
       </c>
-      <c r="O16" t="s">
-        <v>56</v>
-      </c>
       <c r="Q16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R16" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="T16" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="U16">
         <v>100</v>
       </c>
       <c r="V16" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="W16">
         <v>11.76</v>
       </c>
       <c r="Z16" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AA16" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="AD16" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE16" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="3:31">
@@ -1554,184 +1530,220 @@
         <v>35</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G17" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" t="s">
         <v>46</v>
       </c>
-      <c r="H17" t="s">
+      <c r="N17" t="s">
         <v>49</v>
       </c>
-      <c r="N17" t="s">
+      <c r="O17" t="s">
         <v>52</v>
       </c>
-      <c r="O17" t="s">
-        <v>56</v>
-      </c>
       <c r="Q17" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R17" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="T17" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="U17">
         <v>150</v>
       </c>
       <c r="V17" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="W17">
         <v>1.06</v>
       </c>
       <c r="Z17" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AA17" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="AD17" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE17" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="3:31">
       <c r="C18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
         <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>40</v>
+        <v>39</v>
+      </c>
+      <c r="F18" t="s">
+        <v>42</v>
       </c>
       <c r="G18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" t="s">
         <v>47</v>
       </c>
       <c r="N18" t="s">
+        <v>50</v>
+      </c>
+      <c r="O18" t="s">
         <v>53</v>
       </c>
-      <c r="O18" t="s">
-        <v>57</v>
-      </c>
       <c r="Q18" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="R18" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="T18" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="U18">
-        <v>200</v>
+        <v>7000</v>
+      </c>
+      <c r="V18" t="s">
+        <v>73</v>
       </c>
       <c r="W18">
-        <v>5.74</v>
+        <v>39</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>79</v>
       </c>
       <c r="AA18" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="AD18" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE18" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="3:31">
       <c r="C19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
         <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
+        <v>39</v>
+      </c>
+      <c r="F19" t="s">
+        <v>42</v>
       </c>
       <c r="G19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" t="s">
         <v>47</v>
       </c>
       <c r="N19" t="s">
+        <v>50</v>
+      </c>
+      <c r="O19" t="s">
         <v>53</v>
       </c>
-      <c r="O19" t="s">
-        <v>57</v>
-      </c>
       <c r="Q19" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="R19" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="T19" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="U19">
-        <v>200</v>
+        <v>15000</v>
+      </c>
+      <c r="V19" t="s">
+        <v>73</v>
       </c>
       <c r="W19">
-        <v>5.36</v>
+        <v>22</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>79</v>
       </c>
       <c r="AA19" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="AD19" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE19" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="3:31">
       <c r="C20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
         <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>39</v>
+      </c>
+      <c r="F20" t="s">
+        <v>42</v>
       </c>
       <c r="G20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20" t="s">
         <v>47</v>
       </c>
       <c r="N20" t="s">
+        <v>50</v>
+      </c>
+      <c r="O20" t="s">
         <v>53</v>
       </c>
-      <c r="O20" t="s">
-        <v>57</v>
-      </c>
       <c r="Q20" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="R20" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="T20" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="U20">
-        <v>200</v>
+        <v>15000</v>
+      </c>
+      <c r="V20" t="s">
+        <v>73</v>
       </c>
       <c r="W20">
-        <v>3.5</v>
+        <v>23</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>79</v>
       </c>
       <c r="AA20" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="AD20" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE20" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="3:31">
@@ -1739,55 +1751,52 @@
         <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G21" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H21" t="s">
+        <v>47</v>
+      </c>
+      <c r="N21" t="s">
         <v>50</v>
       </c>
-      <c r="N21" t="s">
-        <v>54</v>
-      </c>
       <c r="O21" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="Q21" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="R21" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="T21" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="U21">
-        <v>7000</v>
+        <v>1000</v>
       </c>
       <c r="V21" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="W21">
-        <v>39</v>
+        <v>680</v>
       </c>
       <c r="Z21" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AD21" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE21" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="3:31">
@@ -1795,55 +1804,52 @@
         <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F22" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G22" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H22" t="s">
+        <v>47</v>
+      </c>
+      <c r="N22" t="s">
         <v>50</v>
       </c>
-      <c r="N22" t="s">
-        <v>54</v>
-      </c>
       <c r="O22" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="Q22" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="R22" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="T22" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="U22">
-        <v>15000</v>
+        <v>1000</v>
       </c>
       <c r="V22" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="W22">
-        <v>22</v>
+        <v>600</v>
       </c>
       <c r="Z22" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="AD22" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE22" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="3:31">
@@ -1851,214 +1857,52 @@
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G23" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H23" t="s">
+        <v>47</v>
+      </c>
+      <c r="N23" t="s">
         <v>50</v>
       </c>
-      <c r="N23" t="s">
-        <v>54</v>
-      </c>
       <c r="O23" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="Q23" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="R23" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="T23" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="U23">
-        <v>15000</v>
+        <v>1000</v>
       </c>
       <c r="V23" t="s">
+        <v>73</v>
+      </c>
+      <c r="W23">
+        <v>560</v>
+      </c>
+      <c r="Z23" t="s">
         <v>82</v>
       </c>
-      <c r="W23">
-        <v>23</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA23" t="s">
-        <v>97</v>
-      </c>
       <c r="AD23" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AE23" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="24" spans="3:31">
-      <c r="C24" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" t="s">
-        <v>41</v>
-      </c>
-      <c r="F24" t="s">
-        <v>44</v>
-      </c>
-      <c r="G24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H24" t="s">
-        <v>50</v>
-      </c>
-      <c r="N24" t="s">
-        <v>54</v>
-      </c>
-      <c r="O24" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>61</v>
-      </c>
-      <c r="R24" t="s">
-        <v>62</v>
-      </c>
-      <c r="T24" t="s">
-        <v>80</v>
-      </c>
-      <c r="U24">
-        <v>1000</v>
-      </c>
-      <c r="V24" t="s">
-        <v>82</v>
-      </c>
-      <c r="W24">
-        <v>680</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>89</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>98</v>
-      </c>
-      <c r="AE24" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="3:31">
-      <c r="C25" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" t="s">
-        <v>41</v>
-      </c>
-      <c r="F25" t="s">
-        <v>44</v>
-      </c>
-      <c r="G25" t="s">
-        <v>48</v>
-      </c>
-      <c r="H25" t="s">
-        <v>50</v>
-      </c>
-      <c r="N25" t="s">
-        <v>54</v>
-      </c>
-      <c r="O25" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>61</v>
-      </c>
-      <c r="R25" t="s">
-        <v>62</v>
-      </c>
-      <c r="T25" t="s">
-        <v>80</v>
-      </c>
-      <c r="U25">
-        <v>1000</v>
-      </c>
-      <c r="V25" t="s">
-        <v>82</v>
-      </c>
-      <c r="W25">
-        <v>600</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>90</v>
-      </c>
-      <c r="AD25" t="s">
-        <v>98</v>
-      </c>
-      <c r="AE25" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="26" spans="3:31">
-      <c r="C26" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" t="s">
-        <v>37</v>
-      </c>
-      <c r="E26" t="s">
-        <v>41</v>
-      </c>
-      <c r="F26" t="s">
-        <v>44</v>
-      </c>
-      <c r="G26" t="s">
-        <v>48</v>
-      </c>
-      <c r="H26" t="s">
-        <v>50</v>
-      </c>
-      <c r="N26" t="s">
-        <v>54</v>
-      </c>
-      <c r="O26" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>61</v>
-      </c>
-      <c r="R26" t="s">
-        <v>62</v>
-      </c>
-      <c r="T26" t="s">
-        <v>80</v>
-      </c>
-      <c r="U26">
-        <v>1000</v>
-      </c>
-      <c r="V26" t="s">
-        <v>82</v>
-      </c>
-      <c r="W26">
-        <v>560</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>91</v>
-      </c>
-      <c r="AD26" t="s">
-        <v>98</v>
-      </c>
-      <c r="AE26" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
